--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2749029\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCDC1163-F1A9-4C2E-AF98-37707CB0537F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D34F8CE0-2CA4-48E3-85E7-FE381E2FB3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B3605D9-A3A1-4C06-8E13-F0622F09B54A}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CC162431-8AB2-44ED-B6B8-C1CE112932CA}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="49">
   <si>
     <t>Baia</t>
   </si>
@@ -116,9 +116,6 @@
     <t>LYS 1</t>
   </si>
   <si>
-    <t>KR9</t>
-  </si>
-  <si>
     <t>BZQ 1</t>
   </si>
   <si>
@@ -170,9 +167,6 @@
     <t>QAR 3</t>
   </si>
   <si>
-    <t>ATH 3</t>
-  </si>
-  <si>
     <t>VBS</t>
   </si>
   <si>
@@ -186,6 +180,9 @@
   </si>
   <si>
     <t>FCO</t>
+  </si>
+  <si>
+    <t>DFT 2</t>
   </si>
   <si>
     <t>MXP EXTRA</t>
@@ -563,7 +560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5BA7C7F-CF83-490A-802B-582B30603368}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E3013F6-7AE9-4B21-BB8F-B2B445A67FDF}">
   <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -604,7 +601,7 @@
         <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>0.17218749999999999</v>
+        <v>0.20871527777777779</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -628,6 +625,9 @@
       <c r="C4" s="1">
         <v>0.25</v>
       </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -692,6 +692,9 @@
       <c r="C9" s="1">
         <v>0.20833333333333334</v>
       </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -731,6 +734,9 @@
       <c r="C12" s="1">
         <v>0.21875</v>
       </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
@@ -742,6 +748,9 @@
       <c r="C13" s="1">
         <v>0.19097222222222221</v>
       </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -848,6 +857,9 @@
       <c r="C21" s="1">
         <v>0.40625</v>
       </c>
+      <c r="D21" s="1">
+        <v>9.3368055555555565E-2</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
@@ -926,27 +938,27 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B28" t="s">
         <v>25</v>
       </c>
       <c r="C28" s="1">
-        <v>0.26388888889050577</v>
-      </c>
-      <c r="D28" s="1">
-        <v>2.9201388890505785E-2</v>
+        <v>0.11458333333575865</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B29" t="s">
         <v>26</v>
       </c>
       <c r="C29" s="1">
-        <v>0.11458333333575865</v>
+        <v>8.3333333335758653E-2</v>
       </c>
       <c r="E29" t="s">
         <v>7</v>
@@ -954,13 +966,13 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B30" t="s">
         <v>27</v>
       </c>
       <c r="C30" s="1">
-        <v>8.3333333335758653E-2</v>
+        <v>0.41666666666424135</v>
       </c>
       <c r="E30" t="s">
         <v>7</v>
@@ -968,13 +980,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B31" t="s">
         <v>28</v>
       </c>
       <c r="C31" s="1">
-        <v>0.41666666666424135</v>
+        <v>0.10416666666424135</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -985,32 +1000,32 @@
         <v>29</v>
       </c>
       <c r="C32" s="1">
-        <v>0.10416666666424135</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B33" t="s">
         <v>30</v>
       </c>
       <c r="C33" s="1">
-        <v>0.375</v>
+        <v>0.10416666666424135</v>
+      </c>
+      <c r="E33" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s">
         <v>31</v>
       </c>
       <c r="C34" s="1">
-        <v>0.10416666666424135</v>
+        <v>0.3576388888888889</v>
       </c>
       <c r="E34" t="s">
         <v>7</v>
@@ -1021,10 +1036,10 @@
         <v>337</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="1">
-        <v>0.3576388888888889</v>
+        <v>0.95138888888888884</v>
       </c>
       <c r="E35" t="s">
         <v>7</v>
@@ -1032,13 +1047,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36" s="1">
-        <v>0.95138888888888884</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
@@ -1046,27 +1061,24 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s">
         <v>32</v>
       </c>
       <c r="C37" s="1">
-        <v>0.27083333333333331</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
+        <v>0.41666666666424135</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s">
         <v>33</v>
       </c>
       <c r="C38" s="1">
-        <v>0.41666666666424135</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,12 +1089,15 @@
         <v>34</v>
       </c>
       <c r="C39" s="1">
-        <v>0.4375</v>
+        <v>9.375E-2</v>
+      </c>
+      <c r="E39" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s">
         <v>35</v>
@@ -1096,16 +1111,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s">
         <v>36</v>
       </c>
       <c r="C41" s="1">
-        <v>9.375E-2</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
+        <v>0.4375</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0.16628472222222218</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1116,21 +1131,21 @@
         <v>37</v>
       </c>
       <c r="C42" s="1">
-        <v>0.4375</v>
-      </c>
-      <c r="D42" s="1">
-        <v>0.20280092592592588</v>
+        <v>8.3333333335758653E-2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s">
         <v>38</v>
       </c>
       <c r="C43" s="1">
-        <v>8.3333333335758653E-2</v>
+        <v>0.4375</v>
       </c>
       <c r="E43" t="s">
         <v>7</v>
@@ -1138,13 +1153,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s">
         <v>39</v>
       </c>
       <c r="C44" s="1">
-        <v>0.4375</v>
+        <v>9.375E-2</v>
       </c>
       <c r="E44" t="s">
         <v>7</v>
@@ -1152,16 +1167,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B45" t="s">
         <v>40</v>
       </c>
       <c r="C45" s="1">
-        <v>9.375E-2</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
+        <v>0.41666666666424135</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1172,18 +1184,21 @@
         <v>41</v>
       </c>
       <c r="C46" s="1">
-        <v>0.41666666666424135</v>
+        <v>9.375E-2</v>
+      </c>
+      <c r="E46" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B47" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="1">
-        <v>9.375E-2</v>
+        <v>0.125</v>
       </c>
       <c r="E47" t="s">
         <v>7</v>
@@ -1191,46 +1206,46 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C48" s="1">
-        <v>0.26388888889050577</v>
-      </c>
-      <c r="D48" s="1">
-        <v>4.3078703705320562E-2</v>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="E48" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C49" s="1">
-        <v>0.22916666666666666</v>
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="E49" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B50" t="s">
         <v>44</v>
       </c>
       <c r="C50" s="1">
-        <v>0.125</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B51" t="s">
         <v>44</v>
@@ -1244,13 +1259,13 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C52" s="1">
-        <v>0.27083333333333331</v>
+        <v>0.20833333333333334</v>
       </c>
       <c r="E52" t="s">
         <v>7</v>
@@ -1258,24 +1273,27 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C53" s="1">
-        <v>0.25</v>
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="D53" s="1">
+        <v>4.8217592592592604E-2</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C54" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.1875</v>
       </c>
       <c r="E54" t="s">
         <v>7</v>
@@ -1283,69 +1301,63 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B55" t="s">
         <v>46</v>
       </c>
       <c r="C55" s="1">
-        <v>0.20833333333333334</v>
+        <v>0.5</v>
+      </c>
+      <c r="D55" s="1">
+        <v>0.25655092592592593</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B56" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C56" s="1">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="D56" s="1">
-        <v>8.4745370370370374E-2</v>
+        <v>0.27083333333333331</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>353</v>
+        <v>307</v>
       </c>
       <c r="B57" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C57" s="1">
-        <v>0.1875</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>355</v>
+        <v>306</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="C58" s="1">
-        <v>0.5</v>
+        <v>0.26041666666666669</v>
       </c>
       <c r="D58" s="1">
-        <v>0.2930787037037037</v>
+        <v>1.69675925925926E-2</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="C59" s="1">
-        <v>0.26041666666666669</v>
-      </c>
-      <c r="D59" s="1">
-        <v>5.3495370370370374E-2</v>
+        <v>0.41666666666424135</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1353,13 +1365,13 @@
         <v>337</v>
       </c>
       <c r="B60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C60" s="1">
         <v>0.3576388888888889</v>
       </c>
       <c r="D60" s="1">
-        <v>0.15071759259259257</v>
+        <v>0.11418981481481481</v>
       </c>
     </row>
   </sheetData>
